--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647128</v>
+        <v>122647129</v>
       </c>
       <c r="B3" t="n">
-        <v>90851</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551921</v>
+        <v>551975</v>
       </c>
       <c r="R3" t="n">
-        <v>7246620</v>
+        <v>7246676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647174</v>
+        <v>122647170</v>
       </c>
       <c r="B5" t="n">
-        <v>82443</v>
+        <v>74749</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552044</v>
+        <v>552046</v>
       </c>
       <c r="R5" t="n">
-        <v>7246744</v>
+        <v>7246745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647148</v>
+        <v>122647124</v>
       </c>
       <c r="B6" t="n">
-        <v>78738</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552005</v>
+        <v>551916</v>
       </c>
       <c r="R6" t="n">
-        <v>7246718</v>
+        <v>7246616</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647152</v>
+        <v>122647131</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>90833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552078</v>
+        <v>551931</v>
       </c>
       <c r="R7" t="n">
-        <v>7246829</v>
+        <v>7246621</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647129</v>
+        <v>122647130</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551975</v>
+        <v>551971</v>
       </c>
       <c r="R8" t="n">
-        <v>7246676</v>
+        <v>7246700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647181</v>
+        <v>122647152</v>
       </c>
       <c r="B9" t="n">
-        <v>90829</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552065</v>
+        <v>552078</v>
       </c>
       <c r="R9" t="n">
-        <v>7246777</v>
+        <v>7246829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647130</v>
+        <v>122647150</v>
       </c>
       <c r="B10" t="n">
-        <v>78738</v>
+        <v>74762</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551971</v>
+        <v>552059</v>
       </c>
       <c r="R10" t="n">
-        <v>7246700</v>
+        <v>7246774</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647153</v>
+        <v>122647143</v>
       </c>
       <c r="B11" t="n">
-        <v>79766</v>
+        <v>90851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552097</v>
+        <v>551975</v>
       </c>
       <c r="R11" t="n">
-        <v>7246843</v>
+        <v>7246695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647143</v>
+        <v>122647127</v>
       </c>
       <c r="B12" t="n">
-        <v>90851</v>
+        <v>82443</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551975</v>
+        <v>551916</v>
       </c>
       <c r="R12" t="n">
-        <v>7246695</v>
+        <v>7246618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647127</v>
+        <v>122647149</v>
       </c>
       <c r="B13" t="n">
-        <v>82443</v>
+        <v>78656</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551916</v>
+        <v>551991</v>
       </c>
       <c r="R13" t="n">
-        <v>7246618</v>
+        <v>7246738</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647149</v>
+        <v>122647153</v>
       </c>
       <c r="B14" t="n">
-        <v>78656</v>
+        <v>79766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551991</v>
+        <v>552097</v>
       </c>
       <c r="R14" t="n">
-        <v>7246738</v>
+        <v>7246843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647167</v>
+        <v>122647154</v>
       </c>
       <c r="B15" t="n">
-        <v>90833</v>
+        <v>79738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552013</v>
+        <v>552097</v>
       </c>
       <c r="R15" t="n">
-        <v>7246741</v>
+        <v>7246843</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647151</v>
+        <v>122647148</v>
       </c>
       <c r="B16" t="n">
-        <v>90851</v>
+        <v>78738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552083</v>
+        <v>552005</v>
       </c>
       <c r="R16" t="n">
-        <v>7246812</v>
+        <v>7246718</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647131</v>
+        <v>122647167</v>
       </c>
       <c r="B17" t="n">
         <v>90833</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551931</v>
+        <v>552013</v>
       </c>
       <c r="R17" t="n">
-        <v>7246621</v>
+        <v>7246741</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647154</v>
+        <v>122647128</v>
       </c>
       <c r="B18" t="n">
-        <v>79738</v>
+        <v>90851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552097</v>
+        <v>551921</v>
       </c>
       <c r="R18" t="n">
-        <v>7246843</v>
+        <v>7246620</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647170</v>
+        <v>122647174</v>
       </c>
       <c r="B19" t="n">
-        <v>74749</v>
+        <v>82443</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552046</v>
+        <v>552044</v>
       </c>
       <c r="R19" t="n">
-        <v>7246745</v>
+        <v>7246744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647150</v>
+        <v>122647181</v>
       </c>
       <c r="B20" t="n">
-        <v>74762</v>
+        <v>90829</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552059</v>
+        <v>552065</v>
       </c>
       <c r="R20" t="n">
-        <v>7246774</v>
+        <v>7246777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647124</v>
+        <v>122647151</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>90851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551916</v>
+        <v>552083</v>
       </c>
       <c r="R22" t="n">
-        <v>7246616</v>
+        <v>7246812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647125</v>
+        <v>122647129</v>
       </c>
       <c r="B2" t="n">
-        <v>90847</v>
+        <v>78657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551928</v>
+        <v>551975</v>
       </c>
       <c r="R2" t="n">
-        <v>7246605</v>
+        <v>7246676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647129</v>
+        <v>122647128</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551975</v>
+        <v>551921</v>
       </c>
       <c r="R3" t="n">
-        <v>7246676</v>
+        <v>7246620</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647173</v>
+        <v>122647181</v>
       </c>
       <c r="B4" t="n">
-        <v>90829</v>
+        <v>90830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552049</v>
+        <v>552065</v>
       </c>
       <c r="R4" t="n">
-        <v>7246747</v>
+        <v>7246777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647170</v>
+        <v>122647167</v>
       </c>
       <c r="B5" t="n">
-        <v>74749</v>
+        <v>90834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552046</v>
+        <v>552013</v>
       </c>
       <c r="R5" t="n">
-        <v>7246745</v>
+        <v>7246741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647124</v>
+        <v>122647149</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551916</v>
+        <v>551991</v>
       </c>
       <c r="R6" t="n">
-        <v>7246616</v>
+        <v>7246738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647131</v>
+        <v>122647124</v>
       </c>
       <c r="B7" t="n">
-        <v>90833</v>
+        <v>78657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551931</v>
+        <v>551916</v>
       </c>
       <c r="R7" t="n">
-        <v>7246621</v>
+        <v>7246616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647130</v>
+        <v>122647173</v>
       </c>
       <c r="B8" t="n">
-        <v>78738</v>
+        <v>90830</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551971</v>
+        <v>552049</v>
       </c>
       <c r="R8" t="n">
-        <v>7246700</v>
+        <v>7246747</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>122647152</v>
       </c>
       <c r="B9" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647150</v>
+        <v>122647142</v>
       </c>
       <c r="B10" t="n">
-        <v>74762</v>
+        <v>90852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552059</v>
+        <v>551988</v>
       </c>
       <c r="R10" t="n">
-        <v>7246774</v>
+        <v>7246686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647143</v>
+        <v>122647127</v>
       </c>
       <c r="B11" t="n">
-        <v>90851</v>
+        <v>82444</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551975</v>
+        <v>551916</v>
       </c>
       <c r="R11" t="n">
-        <v>7246695</v>
+        <v>7246618</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647127</v>
+        <v>122647153</v>
       </c>
       <c r="B12" t="n">
-        <v>82443</v>
+        <v>79767</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551916</v>
+        <v>552097</v>
       </c>
       <c r="R12" t="n">
-        <v>7246618</v>
+        <v>7246843</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647149</v>
+        <v>122647143</v>
       </c>
       <c r="B13" t="n">
-        <v>78656</v>
+        <v>90852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551991</v>
+        <v>551975</v>
       </c>
       <c r="R13" t="n">
-        <v>7246738</v>
+        <v>7246695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647153</v>
+        <v>122647125</v>
       </c>
       <c r="B14" t="n">
-        <v>79766</v>
+        <v>90848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552097</v>
+        <v>551928</v>
       </c>
       <c r="R14" t="n">
-        <v>7246843</v>
+        <v>7246605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647154</v>
+        <v>122647150</v>
       </c>
       <c r="B15" t="n">
-        <v>79738</v>
+        <v>74763</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552097</v>
+        <v>552059</v>
       </c>
       <c r="R15" t="n">
-        <v>7246843</v>
+        <v>7246774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647148</v>
+        <v>122647151</v>
       </c>
       <c r="B16" t="n">
-        <v>78738</v>
+        <v>90852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552005</v>
+        <v>552083</v>
       </c>
       <c r="R16" t="n">
-        <v>7246718</v>
+        <v>7246812</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647167</v>
+        <v>122647131</v>
       </c>
       <c r="B17" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552013</v>
+        <v>551931</v>
       </c>
       <c r="R17" t="n">
-        <v>7246741</v>
+        <v>7246621</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647128</v>
+        <v>122647148</v>
       </c>
       <c r="B18" t="n">
-        <v>90851</v>
+        <v>78739</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551921</v>
+        <v>552005</v>
       </c>
       <c r="R18" t="n">
-        <v>7246620</v>
+        <v>7246718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647174</v>
+        <v>122647154</v>
       </c>
       <c r="B19" t="n">
-        <v>82443</v>
+        <v>79739</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552044</v>
+        <v>552097</v>
       </c>
       <c r="R19" t="n">
-        <v>7246744</v>
+        <v>7246843</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647181</v>
+        <v>122647174</v>
       </c>
       <c r="B20" t="n">
-        <v>90829</v>
+        <v>82444</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552065</v>
+        <v>552044</v>
       </c>
       <c r="R20" t="n">
-        <v>7246777</v>
+        <v>7246744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647142</v>
+        <v>122647170</v>
       </c>
       <c r="B21" t="n">
-        <v>90851</v>
+        <v>74750</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551988</v>
+        <v>552046</v>
       </c>
       <c r="R21" t="n">
-        <v>7246686</v>
+        <v>7246745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647151</v>
+        <v>122647130</v>
       </c>
       <c r="B22" t="n">
-        <v>90851</v>
+        <v>78739</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552083</v>
+        <v>551971</v>
       </c>
       <c r="R22" t="n">
-        <v>7246812</v>
+        <v>7246700</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647149</v>
+        <v>122647173</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>90830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551991</v>
+        <v>552049</v>
       </c>
       <c r="R6" t="n">
-        <v>7246738</v>
+        <v>7246747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647124</v>
+        <v>122647149</v>
       </c>
       <c r="B7" t="n">
         <v>78657</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551916</v>
+        <v>551991</v>
       </c>
       <c r="R7" t="n">
-        <v>7246616</v>
+        <v>7246738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647173</v>
+        <v>122647124</v>
       </c>
       <c r="B8" t="n">
-        <v>90830</v>
+        <v>78657</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552049</v>
+        <v>551916</v>
       </c>
       <c r="R8" t="n">
-        <v>7246747</v>
+        <v>7246616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647152</v>
+        <v>122647127</v>
       </c>
       <c r="B9" t="n">
-        <v>78657</v>
+        <v>82444</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552078</v>
+        <v>551916</v>
       </c>
       <c r="R9" t="n">
-        <v>7246829</v>
+        <v>7246618</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647127</v>
+        <v>122647152</v>
       </c>
       <c r="B11" t="n">
-        <v>82444</v>
+        <v>78657</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551916</v>
+        <v>552078</v>
       </c>
       <c r="R11" t="n">
-        <v>7246618</v>
+        <v>7246829</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647129</v>
+        <v>122647131</v>
       </c>
       <c r="B2" t="n">
-        <v>78657</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551975</v>
+        <v>551931</v>
       </c>
       <c r="R2" t="n">
-        <v>7246676</v>
+        <v>7246621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647128</v>
+        <v>122647148</v>
       </c>
       <c r="B3" t="n">
-        <v>90852</v>
+        <v>78742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551921</v>
+        <v>552005</v>
       </c>
       <c r="R3" t="n">
-        <v>7246620</v>
+        <v>7246718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647181</v>
+        <v>122647151</v>
       </c>
       <c r="B4" t="n">
-        <v>90830</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552065</v>
+        <v>552083</v>
       </c>
       <c r="R4" t="n">
-        <v>7246777</v>
+        <v>7246812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647167</v>
+        <v>122647128</v>
       </c>
       <c r="B5" t="n">
-        <v>90834</v>
+        <v>90855</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552013</v>
+        <v>551921</v>
       </c>
       <c r="R5" t="n">
-        <v>7246741</v>
+        <v>7246620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647173</v>
+        <v>122647143</v>
       </c>
       <c r="B6" t="n">
-        <v>90830</v>
+        <v>90855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552049</v>
+        <v>551975</v>
       </c>
       <c r="R6" t="n">
-        <v>7246747</v>
+        <v>7246695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647149</v>
+        <v>122647124</v>
       </c>
       <c r="B7" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551991</v>
+        <v>551916</v>
       </c>
       <c r="R7" t="n">
-        <v>7246738</v>
+        <v>7246616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647124</v>
+        <v>122647174</v>
       </c>
       <c r="B8" t="n">
-        <v>78657</v>
+        <v>82447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551916</v>
+        <v>552044</v>
       </c>
       <c r="R8" t="n">
-        <v>7246616</v>
+        <v>7246744</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647127</v>
+        <v>122647149</v>
       </c>
       <c r="B9" t="n">
-        <v>82444</v>
+        <v>78660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551916</v>
+        <v>551991</v>
       </c>
       <c r="R9" t="n">
-        <v>7246618</v>
+        <v>7246738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647142</v>
+        <v>122647170</v>
       </c>
       <c r="B10" t="n">
-        <v>90852</v>
+        <v>74753</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551988</v>
+        <v>552046</v>
       </c>
       <c r="R10" t="n">
-        <v>7246686</v>
+        <v>7246745</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647152</v>
+        <v>122647181</v>
       </c>
       <c r="B11" t="n">
-        <v>78657</v>
+        <v>90833</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552078</v>
+        <v>552065</v>
       </c>
       <c r="R11" t="n">
-        <v>7246829</v>
+        <v>7246777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647153</v>
+        <v>122647129</v>
       </c>
       <c r="B12" t="n">
-        <v>79767</v>
+        <v>78660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552097</v>
+        <v>551975</v>
       </c>
       <c r="R12" t="n">
-        <v>7246843</v>
+        <v>7246676</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647143</v>
+        <v>122647130</v>
       </c>
       <c r="B13" t="n">
-        <v>90852</v>
+        <v>78742</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551975</v>
+        <v>551971</v>
       </c>
       <c r="R13" t="n">
-        <v>7246695</v>
+        <v>7246700</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647125</v>
+        <v>122647167</v>
       </c>
       <c r="B14" t="n">
-        <v>90848</v>
+        <v>90837</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551928</v>
+        <v>552013</v>
       </c>
       <c r="R14" t="n">
-        <v>7246605</v>
+        <v>7246741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647150</v>
+        <v>122647153</v>
       </c>
       <c r="B15" t="n">
-        <v>74763</v>
+        <v>79770</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552059</v>
+        <v>552097</v>
       </c>
       <c r="R15" t="n">
-        <v>7246774</v>
+        <v>7246843</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647151</v>
+        <v>122647127</v>
       </c>
       <c r="B16" t="n">
-        <v>90852</v>
+        <v>82447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552083</v>
+        <v>551916</v>
       </c>
       <c r="R16" t="n">
-        <v>7246812</v>
+        <v>7246618</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647131</v>
+        <v>122647154</v>
       </c>
       <c r="B17" t="n">
-        <v>90834</v>
+        <v>79742</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551931</v>
+        <v>552097</v>
       </c>
       <c r="R17" t="n">
-        <v>7246621</v>
+        <v>7246843</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647148</v>
+        <v>122647150</v>
       </c>
       <c r="B18" t="n">
-        <v>78739</v>
+        <v>74766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552005</v>
+        <v>552059</v>
       </c>
       <c r="R18" t="n">
-        <v>7246718</v>
+        <v>7246774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647154</v>
+        <v>122647173</v>
       </c>
       <c r="B19" t="n">
-        <v>79739</v>
+        <v>90833</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552097</v>
+        <v>552049</v>
       </c>
       <c r="R19" t="n">
-        <v>7246843</v>
+        <v>7246747</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647174</v>
+        <v>122647125</v>
       </c>
       <c r="B20" t="n">
-        <v>82444</v>
+        <v>90851</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552044</v>
+        <v>551928</v>
       </c>
       <c r="R20" t="n">
-        <v>7246744</v>
+        <v>7246605</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647170</v>
+        <v>122647142</v>
       </c>
       <c r="B21" t="n">
-        <v>74750</v>
+        <v>90855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552046</v>
+        <v>551988</v>
       </c>
       <c r="R21" t="n">
-        <v>7246745</v>
+        <v>7246686</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647130</v>
+        <v>122647152</v>
       </c>
       <c r="B22" t="n">
-        <v>78739</v>
+        <v>78660</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551971</v>
+        <v>552078</v>
       </c>
       <c r="R22" t="n">
-        <v>7246700</v>
+        <v>7246829</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647131</v>
+        <v>122647148</v>
       </c>
       <c r="B2" t="n">
-        <v>90837</v>
+        <v>78742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551931</v>
+        <v>552005</v>
       </c>
       <c r="R2" t="n">
-        <v>7246621</v>
+        <v>7246718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647148</v>
+        <v>122647149</v>
       </c>
       <c r="B3" t="n">
-        <v>78742</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552005</v>
+        <v>551991</v>
       </c>
       <c r="R3" t="n">
-        <v>7246718</v>
+        <v>7246738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647151</v>
+        <v>122647130</v>
       </c>
       <c r="B4" t="n">
-        <v>90855</v>
+        <v>78742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552083</v>
+        <v>551971</v>
       </c>
       <c r="R4" t="n">
-        <v>7246812</v>
+        <v>7246700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647128</v>
+        <v>122647131</v>
       </c>
       <c r="B5" t="n">
-        <v>90855</v>
+        <v>90837</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551921</v>
+        <v>551931</v>
       </c>
       <c r="R5" t="n">
-        <v>7246620</v>
+        <v>7246621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647124</v>
+        <v>122647125</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>90851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551916</v>
+        <v>551928</v>
       </c>
       <c r="R7" t="n">
-        <v>7246616</v>
+        <v>7246605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647174</v>
+        <v>122647170</v>
       </c>
       <c r="B8" t="n">
-        <v>82447</v>
+        <v>74753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552044</v>
+        <v>552046</v>
       </c>
       <c r="R8" t="n">
-        <v>7246744</v>
+        <v>7246745</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647149</v>
+        <v>122647128</v>
       </c>
       <c r="B9" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551991</v>
+        <v>551921</v>
       </c>
       <c r="R9" t="n">
-        <v>7246738</v>
+        <v>7246620</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647170</v>
+        <v>122647174</v>
       </c>
       <c r="B10" t="n">
-        <v>74753</v>
+        <v>82447</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552046</v>
+        <v>552044</v>
       </c>
       <c r="R10" t="n">
-        <v>7246745</v>
+        <v>7246744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647181</v>
+        <v>122647151</v>
       </c>
       <c r="B11" t="n">
-        <v>90833</v>
+        <v>90855</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552065</v>
+        <v>552083</v>
       </c>
       <c r="R11" t="n">
-        <v>7246777</v>
+        <v>7246812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647129</v>
+        <v>122647142</v>
       </c>
       <c r="B12" t="n">
-        <v>78660</v>
+        <v>90855</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551975</v>
+        <v>551988</v>
       </c>
       <c r="R12" t="n">
-        <v>7246676</v>
+        <v>7246686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647130</v>
+        <v>122647181</v>
       </c>
       <c r="B13" t="n">
-        <v>78742</v>
+        <v>90833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551971</v>
+        <v>552065</v>
       </c>
       <c r="R13" t="n">
-        <v>7246700</v>
+        <v>7246777</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647167</v>
+        <v>122647124</v>
       </c>
       <c r="B14" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552013</v>
+        <v>551916</v>
       </c>
       <c r="R14" t="n">
-        <v>7246741</v>
+        <v>7246616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647153</v>
+        <v>122647129</v>
       </c>
       <c r="B15" t="n">
-        <v>79770</v>
+        <v>78660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552097</v>
+        <v>551975</v>
       </c>
       <c r="R15" t="n">
-        <v>7246843</v>
+        <v>7246676</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647127</v>
+        <v>122647154</v>
       </c>
       <c r="B16" t="n">
-        <v>82447</v>
+        <v>79742</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551916</v>
+        <v>552097</v>
       </c>
       <c r="R16" t="n">
-        <v>7246618</v>
+        <v>7246843</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647154</v>
+        <v>122647153</v>
       </c>
       <c r="B17" t="n">
-        <v>79742</v>
+        <v>79770</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647173</v>
+        <v>122647127</v>
       </c>
       <c r="B19" t="n">
-        <v>90833</v>
+        <v>82447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552049</v>
+        <v>551916</v>
       </c>
       <c r="R19" t="n">
-        <v>7246747</v>
+        <v>7246618</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647125</v>
+        <v>122647167</v>
       </c>
       <c r="B20" t="n">
-        <v>90851</v>
+        <v>90837</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551928</v>
+        <v>552013</v>
       </c>
       <c r="R20" t="n">
-        <v>7246605</v>
+        <v>7246741</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647142</v>
+        <v>122647173</v>
       </c>
       <c r="B21" t="n">
-        <v>90855</v>
+        <v>90833</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551988</v>
+        <v>552049</v>
       </c>
       <c r="R21" t="n">
-        <v>7246686</v>
+        <v>7246747</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647125</v>
+        <v>122647170</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>74753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551928</v>
+        <v>552046</v>
       </c>
       <c r="R7" t="n">
-        <v>7246605</v>
+        <v>7246745</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647170</v>
+        <v>122647125</v>
       </c>
       <c r="B8" t="n">
-        <v>74753</v>
+        <v>90851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552046</v>
+        <v>551928</v>
       </c>
       <c r="R8" t="n">
-        <v>7246745</v>
+        <v>7246605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647181</v>
+        <v>122647124</v>
       </c>
       <c r="B13" t="n">
-        <v>90833</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552065</v>
+        <v>551916</v>
       </c>
       <c r="R13" t="n">
-        <v>7246777</v>
+        <v>7246616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647124</v>
+        <v>122647181</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>90833</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551916</v>
+        <v>552065</v>
       </c>
       <c r="R14" t="n">
-        <v>7246616</v>
+        <v>7246777</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647124</v>
+        <v>122647181</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>90833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551916</v>
+        <v>552065</v>
       </c>
       <c r="R13" t="n">
-        <v>7246616</v>
+        <v>7246777</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647181</v>
+        <v>122647124</v>
       </c>
       <c r="B14" t="n">
-        <v>90833</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552065</v>
+        <v>551916</v>
       </c>
       <c r="R14" t="n">
-        <v>7246777</v>
+        <v>7246616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647170</v>
+        <v>122647125</v>
       </c>
       <c r="B7" t="n">
-        <v>74753</v>
+        <v>90851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552046</v>
+        <v>551928</v>
       </c>
       <c r="R7" t="n">
-        <v>7246745</v>
+        <v>7246605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647125</v>
+        <v>122647170</v>
       </c>
       <c r="B8" t="n">
-        <v>90851</v>
+        <v>74753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551928</v>
+        <v>552046</v>
       </c>
       <c r="R8" t="n">
-        <v>7246605</v>
+        <v>7246745</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647181</v>
+        <v>122647124</v>
       </c>
       <c r="B13" t="n">
-        <v>90833</v>
+        <v>78660</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552065</v>
+        <v>551916</v>
       </c>
       <c r="R13" t="n">
-        <v>7246777</v>
+        <v>7246616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647124</v>
+        <v>122647181</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>90833</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551916</v>
+        <v>552065</v>
       </c>
       <c r="R14" t="n">
-        <v>7246616</v>
+        <v>7246777</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647149</v>
+        <v>122647131</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551991</v>
+        <v>551931</v>
       </c>
       <c r="R3" t="n">
-        <v>7246738</v>
+        <v>7246621</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647131</v>
+        <v>122647149</v>
       </c>
       <c r="B5" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551931</v>
+        <v>551991</v>
       </c>
       <c r="R5" t="n">
-        <v>7246621</v>
+        <v>7246738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647131</v>
+        <v>122647149</v>
       </c>
       <c r="B3" t="n">
-        <v>90837</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551931</v>
+        <v>551991</v>
       </c>
       <c r="R3" t="n">
-        <v>7246621</v>
+        <v>7246738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647149</v>
+        <v>122647131</v>
       </c>
       <c r="B5" t="n">
-        <v>78660</v>
+        <v>90837</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551991</v>
+        <v>551931</v>
       </c>
       <c r="R5" t="n">
-        <v>7246738</v>
+        <v>7246621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647124</v>
+        <v>122647181</v>
       </c>
       <c r="B13" t="n">
-        <v>78660</v>
+        <v>90833</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551916</v>
+        <v>552065</v>
       </c>
       <c r="R13" t="n">
-        <v>7246616</v>
+        <v>7246777</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647181</v>
+        <v>122647124</v>
       </c>
       <c r="B14" t="n">
-        <v>90833</v>
+        <v>78660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552065</v>
+        <v>551916</v>
       </c>
       <c r="R14" t="n">
-        <v>7246777</v>
+        <v>7246616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647148</v>
+        <v>122647129</v>
       </c>
       <c r="B2" t="n">
-        <v>78742</v>
+        <v>78762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552005</v>
+        <v>551975</v>
       </c>
       <c r="R2" t="n">
-        <v>7246718</v>
+        <v>7246676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647149</v>
+        <v>122647174</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>82549</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551991</v>
+        <v>552044</v>
       </c>
       <c r="R3" t="n">
-        <v>7246738</v>
+        <v>7246744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647130</v>
+        <v>122647153</v>
       </c>
       <c r="B4" t="n">
-        <v>78742</v>
+        <v>79872</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551971</v>
+        <v>552097</v>
       </c>
       <c r="R4" t="n">
-        <v>7246700</v>
+        <v>7246843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647131</v>
+        <v>122647181</v>
       </c>
       <c r="B5" t="n">
-        <v>90837</v>
+        <v>90936</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551931</v>
+        <v>552065</v>
       </c>
       <c r="R5" t="n">
-        <v>7246621</v>
+        <v>7246777</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647143</v>
+        <v>122647127</v>
       </c>
       <c r="B6" t="n">
-        <v>90855</v>
+        <v>82549</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551975</v>
+        <v>551916</v>
       </c>
       <c r="R6" t="n">
-        <v>7246695</v>
+        <v>7246618</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647125</v>
+        <v>122647142</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>90958</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551928</v>
+        <v>551988</v>
       </c>
       <c r="R7" t="n">
-        <v>7246605</v>
+        <v>7246686</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647170</v>
+        <v>122647125</v>
       </c>
       <c r="B8" t="n">
-        <v>74753</v>
+        <v>90954</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552046</v>
+        <v>551928</v>
       </c>
       <c r="R8" t="n">
-        <v>7246745</v>
+        <v>7246605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647128</v>
+        <v>122647151</v>
       </c>
       <c r="B9" t="n">
-        <v>90855</v>
+        <v>90958</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551921</v>
+        <v>552083</v>
       </c>
       <c r="R9" t="n">
-        <v>7246620</v>
+        <v>7246812</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647174</v>
+        <v>122647167</v>
       </c>
       <c r="B10" t="n">
-        <v>82447</v>
+        <v>90940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552044</v>
+        <v>552013</v>
       </c>
       <c r="R10" t="n">
-        <v>7246744</v>
+        <v>7246741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647151</v>
+        <v>122647143</v>
       </c>
       <c r="B11" t="n">
-        <v>90855</v>
+        <v>90958</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552083</v>
+        <v>551975</v>
       </c>
       <c r="R11" t="n">
-        <v>7246812</v>
+        <v>7246695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647142</v>
+        <v>122647150</v>
       </c>
       <c r="B12" t="n">
-        <v>90855</v>
+        <v>74868</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551988</v>
+        <v>552059</v>
       </c>
       <c r="R12" t="n">
-        <v>7246686</v>
+        <v>7246774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647181</v>
+        <v>122647128</v>
       </c>
       <c r="B13" t="n">
-        <v>90833</v>
+        <v>90958</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552065</v>
+        <v>551921</v>
       </c>
       <c r="R13" t="n">
-        <v>7246777</v>
+        <v>7246620</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647124</v>
+        <v>122647149</v>
       </c>
       <c r="B14" t="n">
-        <v>78660</v>
+        <v>78762</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551916</v>
+        <v>551991</v>
       </c>
       <c r="R14" t="n">
-        <v>7246616</v>
+        <v>7246738</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647129</v>
+        <v>122647170</v>
       </c>
       <c r="B15" t="n">
-        <v>78660</v>
+        <v>74855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551975</v>
+        <v>552046</v>
       </c>
       <c r="R15" t="n">
-        <v>7246676</v>
+        <v>7246745</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647154</v>
+        <v>122647124</v>
       </c>
       <c r="B16" t="n">
-        <v>79742</v>
+        <v>78762</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552097</v>
+        <v>551916</v>
       </c>
       <c r="R16" t="n">
-        <v>7246843</v>
+        <v>7246616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647153</v>
+        <v>122647152</v>
       </c>
       <c r="B17" t="n">
-        <v>79770</v>
+        <v>78762</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552097</v>
+        <v>552078</v>
       </c>
       <c r="R17" t="n">
-        <v>7246843</v>
+        <v>7246829</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647150</v>
+        <v>122647130</v>
       </c>
       <c r="B18" t="n">
-        <v>74766</v>
+        <v>78844</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552059</v>
+        <v>551971</v>
       </c>
       <c r="R18" t="n">
-        <v>7246774</v>
+        <v>7246700</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647127</v>
+        <v>122647131</v>
       </c>
       <c r="B19" t="n">
-        <v>82447</v>
+        <v>90940</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551916</v>
+        <v>551931</v>
       </c>
       <c r="R19" t="n">
-        <v>7246618</v>
+        <v>7246621</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647167</v>
+        <v>122647173</v>
       </c>
       <c r="B20" t="n">
-        <v>90837</v>
+        <v>90936</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552013</v>
+        <v>552049</v>
       </c>
       <c r="R20" t="n">
-        <v>7246741</v>
+        <v>7246747</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647173</v>
+        <v>122647148</v>
       </c>
       <c r="B21" t="n">
-        <v>90833</v>
+        <v>78844</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552049</v>
+        <v>552005</v>
       </c>
       <c r="R21" t="n">
-        <v>7246747</v>
+        <v>7246718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647152</v>
+        <v>122647154</v>
       </c>
       <c r="B22" t="n">
-        <v>78660</v>
+        <v>79844</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552078</v>
+        <v>552097</v>
       </c>
       <c r="R22" t="n">
-        <v>7246829</v>
+        <v>7246843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647167</v>
+        <v>122647143</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>90958</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552013</v>
+        <v>551975</v>
       </c>
       <c r="R10" t="n">
-        <v>7246741</v>
+        <v>7246695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647143</v>
+        <v>122647167</v>
       </c>
       <c r="B11" t="n">
-        <v>90958</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551975</v>
+        <v>552013</v>
       </c>
       <c r="R11" t="n">
-        <v>7246695</v>
+        <v>7246741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647129</v>
+        <v>122647173</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>90940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551975</v>
+        <v>552049</v>
       </c>
       <c r="R2" t="n">
-        <v>7246676</v>
+        <v>7246747</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647174</v>
+        <v>122647142</v>
       </c>
       <c r="B3" t="n">
-        <v>82549</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552044</v>
+        <v>551988</v>
       </c>
       <c r="R3" t="n">
-        <v>7246744</v>
+        <v>7246686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647153</v>
+        <v>122647181</v>
       </c>
       <c r="B4" t="n">
-        <v>79872</v>
+        <v>90940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552097</v>
+        <v>552065</v>
       </c>
       <c r="R4" t="n">
-        <v>7246843</v>
+        <v>7246777</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647181</v>
+        <v>122647128</v>
       </c>
       <c r="B5" t="n">
-        <v>90936</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552065</v>
+        <v>551921</v>
       </c>
       <c r="R5" t="n">
-        <v>7246777</v>
+        <v>7246620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647127</v>
+        <v>122647154</v>
       </c>
       <c r="B6" t="n">
-        <v>82549</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551916</v>
+        <v>552097</v>
       </c>
       <c r="R6" t="n">
-        <v>7246618</v>
+        <v>7246843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647142</v>
+        <v>122647149</v>
       </c>
       <c r="B7" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551988</v>
+        <v>551991</v>
       </c>
       <c r="R7" t="n">
-        <v>7246686</v>
+        <v>7246738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647125</v>
+        <v>122647127</v>
       </c>
       <c r="B8" t="n">
-        <v>90954</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551928</v>
+        <v>551916</v>
       </c>
       <c r="R8" t="n">
-        <v>7246605</v>
+        <v>7246618</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647151</v>
+        <v>122647152</v>
       </c>
       <c r="B9" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552083</v>
+        <v>552078</v>
       </c>
       <c r="R9" t="n">
-        <v>7246812</v>
+        <v>7246829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647143</v>
+        <v>122647174</v>
       </c>
       <c r="B10" t="n">
-        <v>90958</v>
+        <v>82553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551975</v>
+        <v>552044</v>
       </c>
       <c r="R10" t="n">
-        <v>7246695</v>
+        <v>7246744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647167</v>
+        <v>122647148</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>78848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552013</v>
+        <v>552005</v>
       </c>
       <c r="R11" t="n">
-        <v>7246741</v>
+        <v>7246718</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647150</v>
+        <v>122647167</v>
       </c>
       <c r="B12" t="n">
-        <v>74868</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552059</v>
+        <v>552013</v>
       </c>
       <c r="R12" t="n">
-        <v>7246774</v>
+        <v>7246741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647128</v>
+        <v>122647150</v>
       </c>
       <c r="B13" t="n">
-        <v>90958</v>
+        <v>74868</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551921</v>
+        <v>552059</v>
       </c>
       <c r="R13" t="n">
-        <v>7246620</v>
+        <v>7246774</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647149</v>
+        <v>122647151</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551991</v>
+        <v>552083</v>
       </c>
       <c r="R14" t="n">
-        <v>7246738</v>
+        <v>7246812</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647124</v>
+        <v>122647153</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>79876</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551916</v>
+        <v>552097</v>
       </c>
       <c r="R16" t="n">
-        <v>7246616</v>
+        <v>7246843</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647152</v>
+        <v>122647143</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552078</v>
+        <v>551975</v>
       </c>
       <c r="R17" t="n">
-        <v>7246829</v>
+        <v>7246695</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2374,7 +2374,7 @@
         <v>122647130</v>
       </c>
       <c r="B18" t="n">
-        <v>78844</v>
+        <v>78848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647131</v>
+        <v>122647125</v>
       </c>
       <c r="B19" t="n">
-        <v>90940</v>
+        <v>90958</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551931</v>
+        <v>551928</v>
       </c>
       <c r="R19" t="n">
-        <v>7246621</v>
+        <v>7246605</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647173</v>
+        <v>122647129</v>
       </c>
       <c r="B20" t="n">
-        <v>90936</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552049</v>
+        <v>551975</v>
       </c>
       <c r="R20" t="n">
-        <v>7246747</v>
+        <v>7246676</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647148</v>
+        <v>122647131</v>
       </c>
       <c r="B21" t="n">
-        <v>78844</v>
+        <v>90944</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552005</v>
+        <v>551931</v>
       </c>
       <c r="R21" t="n">
-        <v>7246718</v>
+        <v>7246621</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647154</v>
+        <v>122647124</v>
       </c>
       <c r="B22" t="n">
-        <v>79844</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552097</v>
+        <v>551916</v>
       </c>
       <c r="R22" t="n">
-        <v>7246843</v>
+        <v>7246616</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647154</v>
+        <v>122647149</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552097</v>
+        <v>551991</v>
       </c>
       <c r="R6" t="n">
-        <v>7246843</v>
+        <v>7246738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647149</v>
+        <v>122647154</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551991</v>
+        <v>552097</v>
       </c>
       <c r="R7" t="n">
-        <v>7246738</v>
+        <v>7246843</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647129</v>
+        <v>122647131</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551975</v>
+        <v>551931</v>
       </c>
       <c r="R20" t="n">
-        <v>7246676</v>
+        <v>7246621</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647131</v>
+        <v>122647129</v>
       </c>
       <c r="B21" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551931</v>
+        <v>551975</v>
       </c>
       <c r="R21" t="n">
-        <v>7246621</v>
+        <v>7246676</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647173</v>
+        <v>122647130</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>78848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552049</v>
+        <v>551971</v>
       </c>
       <c r="R2" t="n">
-        <v>7246747</v>
+        <v>7246700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647142</v>
+        <v>122647167</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551988</v>
+        <v>552013</v>
       </c>
       <c r="R3" t="n">
-        <v>7246686</v>
+        <v>7246741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647181</v>
+        <v>122647152</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552065</v>
+        <v>552078</v>
       </c>
       <c r="R4" t="n">
-        <v>7246777</v>
+        <v>7246829</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647128</v>
+        <v>122647170</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>74855</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551921</v>
+        <v>552046</v>
       </c>
       <c r="R5" t="n">
-        <v>7246620</v>
+        <v>7246745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647149</v>
+        <v>122647129</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551991</v>
+        <v>551975</v>
       </c>
       <c r="R6" t="n">
-        <v>7246738</v>
+        <v>7246676</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647154</v>
+        <v>122647174</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>82553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552097</v>
+        <v>552044</v>
       </c>
       <c r="R7" t="n">
-        <v>7246843</v>
+        <v>7246744</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647127</v>
+        <v>122647154</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551916</v>
+        <v>552097</v>
       </c>
       <c r="R8" t="n">
-        <v>7246618</v>
+        <v>7246843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647152</v>
+        <v>122647131</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552078</v>
+        <v>551931</v>
       </c>
       <c r="R9" t="n">
-        <v>7246829</v>
+        <v>7246621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647174</v>
+        <v>122647125</v>
       </c>
       <c r="B10" t="n">
-        <v>82553</v>
+        <v>90958</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552044</v>
+        <v>551928</v>
       </c>
       <c r="R10" t="n">
-        <v>7246744</v>
+        <v>7246605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647148</v>
+        <v>122647124</v>
       </c>
       <c r="B11" t="n">
-        <v>78848</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552005</v>
+        <v>551916</v>
       </c>
       <c r="R11" t="n">
-        <v>7246718</v>
+        <v>7246616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647167</v>
+        <v>122647150</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>74868</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552013</v>
+        <v>552059</v>
       </c>
       <c r="R12" t="n">
-        <v>7246741</v>
+        <v>7246774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647150</v>
+        <v>122647148</v>
       </c>
       <c r="B13" t="n">
-        <v>74868</v>
+        <v>78848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552059</v>
+        <v>552005</v>
       </c>
       <c r="R13" t="n">
-        <v>7246774</v>
+        <v>7246718</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647170</v>
+        <v>122647149</v>
       </c>
       <c r="B15" t="n">
-        <v>74855</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552046</v>
+        <v>551991</v>
       </c>
       <c r="R15" t="n">
-        <v>7246745</v>
+        <v>7246738</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647153</v>
+        <v>122647143</v>
       </c>
       <c r="B16" t="n">
-        <v>79876</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552097</v>
+        <v>551975</v>
       </c>
       <c r="R16" t="n">
-        <v>7246843</v>
+        <v>7246695</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647143</v>
+        <v>122647173</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>90940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551975</v>
+        <v>552049</v>
       </c>
       <c r="R17" t="n">
-        <v>7246695</v>
+        <v>7246747</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647130</v>
+        <v>122647127</v>
       </c>
       <c r="B18" t="n">
-        <v>78848</v>
+        <v>82553</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551971</v>
+        <v>551916</v>
       </c>
       <c r="R18" t="n">
-        <v>7246700</v>
+        <v>7246618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647125</v>
+        <v>122647142</v>
       </c>
       <c r="B19" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551928</v>
+        <v>551988</v>
       </c>
       <c r="R19" t="n">
-        <v>7246605</v>
+        <v>7246686</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647131</v>
+        <v>122647153</v>
       </c>
       <c r="B20" t="n">
-        <v>90944</v>
+        <v>79876</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551931</v>
+        <v>552097</v>
       </c>
       <c r="R20" t="n">
-        <v>7246621</v>
+        <v>7246843</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647129</v>
+        <v>122647181</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551975</v>
+        <v>552065</v>
       </c>
       <c r="R21" t="n">
-        <v>7246676</v>
+        <v>7246777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647124</v>
+        <v>122647128</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551916</v>
+        <v>551921</v>
       </c>
       <c r="R22" t="n">
-        <v>7246616</v>
+        <v>7246620</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647130</v>
+        <v>122647128</v>
       </c>
       <c r="B2" t="n">
-        <v>78848</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551971</v>
+        <v>551921</v>
       </c>
       <c r="R2" t="n">
-        <v>7246700</v>
+        <v>7246620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647167</v>
+        <v>122647143</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552013</v>
+        <v>551975</v>
       </c>
       <c r="R3" t="n">
-        <v>7246741</v>
+        <v>7246695</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647152</v>
+        <v>122647154</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552078</v>
+        <v>552097</v>
       </c>
       <c r="R4" t="n">
-        <v>7246829</v>
+        <v>7246843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647170</v>
+        <v>122647130</v>
       </c>
       <c r="B5" t="n">
-        <v>74855</v>
+        <v>78848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552046</v>
+        <v>551971</v>
       </c>
       <c r="R5" t="n">
-        <v>7246745</v>
+        <v>7246700</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647129</v>
+        <v>122647127</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551975</v>
+        <v>551916</v>
       </c>
       <c r="R6" t="n">
-        <v>7246676</v>
+        <v>7246618</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647174</v>
+        <v>122647142</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552044</v>
+        <v>551988</v>
       </c>
       <c r="R7" t="n">
-        <v>7246744</v>
+        <v>7246686</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647154</v>
+        <v>122647149</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552097</v>
+        <v>551991</v>
       </c>
       <c r="R8" t="n">
-        <v>7246843</v>
+        <v>7246738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647131</v>
+        <v>122647174</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>82553</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551931</v>
+        <v>552044</v>
       </c>
       <c r="R9" t="n">
-        <v>7246621</v>
+        <v>7246744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647125</v>
+        <v>122647167</v>
       </c>
       <c r="B10" t="n">
-        <v>90958</v>
+        <v>90944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551928</v>
+        <v>552013</v>
       </c>
       <c r="R10" t="n">
-        <v>7246605</v>
+        <v>7246741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647124</v>
+        <v>122647173</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551916</v>
+        <v>552049</v>
       </c>
       <c r="R11" t="n">
-        <v>7246616</v>
+        <v>7246747</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647150</v>
+        <v>122647129</v>
       </c>
       <c r="B12" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552059</v>
+        <v>551975</v>
       </c>
       <c r="R12" t="n">
-        <v>7246774</v>
+        <v>7246676</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647148</v>
+        <v>122647124</v>
       </c>
       <c r="B13" t="n">
-        <v>78848</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552005</v>
+        <v>551916</v>
       </c>
       <c r="R13" t="n">
-        <v>7246718</v>
+        <v>7246616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647151</v>
+        <v>122647170</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>74855</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552083</v>
+        <v>552046</v>
       </c>
       <c r="R14" t="n">
-        <v>7246812</v>
+        <v>7246745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647149</v>
+        <v>122647125</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>90958</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551991</v>
+        <v>551928</v>
       </c>
       <c r="R15" t="n">
-        <v>7246738</v>
+        <v>7246605</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647143</v>
+        <v>122647131</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551975</v>
+        <v>551931</v>
       </c>
       <c r="R16" t="n">
-        <v>7246695</v>
+        <v>7246621</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647173</v>
+        <v>122647181</v>
       </c>
       <c r="B17" t="n">
         <v>90940</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552049</v>
+        <v>552065</v>
       </c>
       <c r="R17" t="n">
-        <v>7246747</v>
+        <v>7246777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647127</v>
+        <v>122647148</v>
       </c>
       <c r="B18" t="n">
-        <v>82553</v>
+        <v>78848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551916</v>
+        <v>552005</v>
       </c>
       <c r="R18" t="n">
-        <v>7246618</v>
+        <v>7246718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647142</v>
+        <v>122647153</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551988</v>
+        <v>552097</v>
       </c>
       <c r="R19" t="n">
-        <v>7246686</v>
+        <v>7246843</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647153</v>
+        <v>122647150</v>
       </c>
       <c r="B20" t="n">
-        <v>79876</v>
+        <v>74868</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552097</v>
+        <v>552059</v>
       </c>
       <c r="R20" t="n">
-        <v>7246843</v>
+        <v>7246774</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647181</v>
+        <v>122647151</v>
       </c>
       <c r="B21" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552065</v>
+        <v>552083</v>
       </c>
       <c r="R21" t="n">
-        <v>7246777</v>
+        <v>7246812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647128</v>
+        <v>122647152</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551921</v>
+        <v>552078</v>
       </c>
       <c r="R22" t="n">
-        <v>7246620</v>
+        <v>7246829</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647128</v>
+        <v>122647154</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551921</v>
+        <v>552097</v>
       </c>
       <c r="R2" t="n">
-        <v>7246620</v>
+        <v>7246843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647143</v>
+        <v>122647142</v>
       </c>
       <c r="B3" t="n">
         <v>90962</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551975</v>
+        <v>551988</v>
       </c>
       <c r="R3" t="n">
-        <v>7246695</v>
+        <v>7246686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647154</v>
+        <v>122647173</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>90940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552097</v>
+        <v>552049</v>
       </c>
       <c r="R4" t="n">
-        <v>7246843</v>
+        <v>7246747</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647130</v>
+        <v>122647153</v>
       </c>
       <c r="B5" t="n">
-        <v>78848</v>
+        <v>79876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551971</v>
+        <v>552097</v>
       </c>
       <c r="R5" t="n">
-        <v>7246700</v>
+        <v>7246843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647127</v>
+        <v>122647149</v>
       </c>
       <c r="B6" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551916</v>
+        <v>551991</v>
       </c>
       <c r="R6" t="n">
-        <v>7246618</v>
+        <v>7246738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647142</v>
+        <v>122647125</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>90958</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551988</v>
+        <v>551928</v>
       </c>
       <c r="R7" t="n">
-        <v>7246686</v>
+        <v>7246605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647149</v>
+        <v>122647131</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551991</v>
+        <v>551931</v>
       </c>
       <c r="R8" t="n">
-        <v>7246738</v>
+        <v>7246621</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647174</v>
+        <v>122647124</v>
       </c>
       <c r="B9" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552044</v>
+        <v>551916</v>
       </c>
       <c r="R9" t="n">
-        <v>7246744</v>
+        <v>7246616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647167</v>
+        <v>122647127</v>
       </c>
       <c r="B10" t="n">
-        <v>90944</v>
+        <v>82553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552013</v>
+        <v>551916</v>
       </c>
       <c r="R10" t="n">
-        <v>7246741</v>
+        <v>7246618</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647173</v>
+        <v>122647150</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>74868</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552049</v>
+        <v>552059</v>
       </c>
       <c r="R11" t="n">
-        <v>7246747</v>
+        <v>7246774</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647129</v>
+        <v>122647174</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551975</v>
+        <v>552044</v>
       </c>
       <c r="R12" t="n">
-        <v>7246676</v>
+        <v>7246744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647124</v>
+        <v>122647151</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551916</v>
+        <v>552083</v>
       </c>
       <c r="R13" t="n">
-        <v>7246616</v>
+        <v>7246812</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647170</v>
+        <v>122647128</v>
       </c>
       <c r="B14" t="n">
-        <v>74855</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552046</v>
+        <v>551921</v>
       </c>
       <c r="R14" t="n">
-        <v>7246745</v>
+        <v>7246620</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647125</v>
+        <v>122647129</v>
       </c>
       <c r="B15" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551928</v>
+        <v>551975</v>
       </c>
       <c r="R15" t="n">
-        <v>7246605</v>
+        <v>7246676</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647131</v>
+        <v>122647181</v>
       </c>
       <c r="B16" t="n">
-        <v>90944</v>
+        <v>90940</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551931</v>
+        <v>552065</v>
       </c>
       <c r="R16" t="n">
-        <v>7246621</v>
+        <v>7246777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647181</v>
+        <v>122647148</v>
       </c>
       <c r="B17" t="n">
-        <v>90940</v>
+        <v>78848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552065</v>
+        <v>552005</v>
       </c>
       <c r="R17" t="n">
-        <v>7246777</v>
+        <v>7246718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647148</v>
+        <v>122647143</v>
       </c>
       <c r="B18" t="n">
-        <v>78848</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552005</v>
+        <v>551975</v>
       </c>
       <c r="R18" t="n">
-        <v>7246718</v>
+        <v>7246695</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647153</v>
+        <v>122647152</v>
       </c>
       <c r="B19" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552097</v>
+        <v>552078</v>
       </c>
       <c r="R19" t="n">
-        <v>7246843</v>
+        <v>7246829</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647150</v>
+        <v>122647130</v>
       </c>
       <c r="B20" t="n">
-        <v>74868</v>
+        <v>78848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552059</v>
+        <v>551971</v>
       </c>
       <c r="R20" t="n">
-        <v>7246774</v>
+        <v>7246700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647151</v>
+        <v>122647170</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>74855</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552083</v>
+        <v>552046</v>
       </c>
       <c r="R21" t="n">
-        <v>7246812</v>
+        <v>7246745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647152</v>
+        <v>122647167</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552078</v>
+        <v>552013</v>
       </c>
       <c r="R22" t="n">
-        <v>7246829</v>
+        <v>7246741</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647152</v>
+        <v>122647130</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>78848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552078</v>
+        <v>551971</v>
       </c>
       <c r="R19" t="n">
-        <v>7246829</v>
+        <v>7246700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647130</v>
+        <v>122647152</v>
       </c>
       <c r="B20" t="n">
-        <v>78848</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551971</v>
+        <v>552078</v>
       </c>
       <c r="R20" t="n">
-        <v>7246700</v>
+        <v>7246829</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647174</v>
+        <v>122647151</v>
       </c>
       <c r="B12" t="n">
-        <v>82553</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552044</v>
+        <v>552083</v>
       </c>
       <c r="R12" t="n">
-        <v>7246744</v>
+        <v>7246812</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647151</v>
+        <v>122647174</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552083</v>
+        <v>552044</v>
       </c>
       <c r="R13" t="n">
-        <v>7246812</v>
+        <v>7246744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647130</v>
+        <v>122647152</v>
       </c>
       <c r="B19" t="n">
-        <v>78848</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551971</v>
+        <v>552078</v>
       </c>
       <c r="R19" t="n">
-        <v>7246700</v>
+        <v>7246829</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647152</v>
+        <v>122647130</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552078</v>
+        <v>551971</v>
       </c>
       <c r="R20" t="n">
-        <v>7246829</v>
+        <v>7246700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647154</v>
+        <v>122647174</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552097</v>
+        <v>552044</v>
       </c>
       <c r="R2" t="n">
-        <v>7246843</v>
+        <v>7246744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647142</v>
+        <v>122647124</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551988</v>
+        <v>551916</v>
       </c>
       <c r="R3" t="n">
-        <v>7246686</v>
+        <v>7246616</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647173</v>
+        <v>122647127</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552049</v>
+        <v>551916</v>
       </c>
       <c r="R4" t="n">
-        <v>7246747</v>
+        <v>7246618</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647153</v>
+        <v>122647154</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647149</v>
+        <v>122647142</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551991</v>
+        <v>551988</v>
       </c>
       <c r="R6" t="n">
-        <v>7246738</v>
+        <v>7246686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647125</v>
+        <v>122647148</v>
       </c>
       <c r="B7" t="n">
-        <v>90958</v>
+        <v>78848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551928</v>
+        <v>552005</v>
       </c>
       <c r="R7" t="n">
-        <v>7246605</v>
+        <v>7246718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647131</v>
+        <v>122647149</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551931</v>
+        <v>551991</v>
       </c>
       <c r="R8" t="n">
-        <v>7246621</v>
+        <v>7246738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647124</v>
+        <v>122647131</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551916</v>
+        <v>551931</v>
       </c>
       <c r="R9" t="n">
-        <v>7246616</v>
+        <v>7246621</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647127</v>
+        <v>122647129</v>
       </c>
       <c r="B10" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551916</v>
+        <v>551975</v>
       </c>
       <c r="R10" t="n">
-        <v>7246618</v>
+        <v>7246676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647150</v>
+        <v>122647170</v>
       </c>
       <c r="B11" t="n">
-        <v>74868</v>
+        <v>74855</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1467</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552059</v>
+        <v>552046</v>
       </c>
       <c r="R11" t="n">
-        <v>7246774</v>
+        <v>7246745</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647151</v>
+        <v>122647143</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552083</v>
+        <v>551975</v>
       </c>
       <c r="R12" t="n">
-        <v>7246812</v>
+        <v>7246695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647174</v>
+        <v>122647152</v>
       </c>
       <c r="B13" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552044</v>
+        <v>552078</v>
       </c>
       <c r="R13" t="n">
-        <v>7246744</v>
+        <v>7246829</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647128</v>
+        <v>122647153</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551921</v>
+        <v>552097</v>
       </c>
       <c r="R14" t="n">
-        <v>7246620</v>
+        <v>7246843</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647129</v>
+        <v>122647150</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>74868</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>551975</v>
+        <v>552059</v>
       </c>
       <c r="R15" t="n">
-        <v>7246676</v>
+        <v>7246774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647181</v>
+        <v>122647167</v>
       </c>
       <c r="B16" t="n">
-        <v>90940</v>
+        <v>90952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552065</v>
+        <v>552013</v>
       </c>
       <c r="R16" t="n">
-        <v>7246777</v>
+        <v>7246741</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647148</v>
+        <v>122647181</v>
       </c>
       <c r="B17" t="n">
-        <v>78848</v>
+        <v>90948</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552005</v>
+        <v>552065</v>
       </c>
       <c r="R17" t="n">
-        <v>7246718</v>
+        <v>7246777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647143</v>
+        <v>122647130</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>78848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551975</v>
+        <v>551971</v>
       </c>
       <c r="R18" t="n">
-        <v>7246695</v>
+        <v>7246700</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647152</v>
+        <v>122647128</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552078</v>
+        <v>551921</v>
       </c>
       <c r="R19" t="n">
-        <v>7246829</v>
+        <v>7246620</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647130</v>
+        <v>122647173</v>
       </c>
       <c r="B20" t="n">
-        <v>78848</v>
+        <v>90948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551971</v>
+        <v>552049</v>
       </c>
       <c r="R20" t="n">
-        <v>7246700</v>
+        <v>7246747</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647170</v>
+        <v>122647125</v>
       </c>
       <c r="B21" t="n">
-        <v>74855</v>
+        <v>90966</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552046</v>
+        <v>551928</v>
       </c>
       <c r="R21" t="n">
-        <v>7246745</v>
+        <v>7246605</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647167</v>
+        <v>122647151</v>
       </c>
       <c r="B22" t="n">
-        <v>90944</v>
+        <v>90970</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552013</v>
+        <v>552083</v>
       </c>
       <c r="R22" t="n">
-        <v>7246741</v>
+        <v>7246812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647152</v>
+        <v>122647153</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552078</v>
+        <v>552097</v>
       </c>
       <c r="R13" t="n">
-        <v>7246829</v>
+        <v>7246843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647153</v>
+        <v>122647152</v>
       </c>
       <c r="B14" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552097</v>
+        <v>552078</v>
       </c>
       <c r="R14" t="n">
-        <v>7246843</v>
+        <v>7246829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647174</v>
+        <v>122647153</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>79876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552044</v>
+        <v>552097</v>
       </c>
       <c r="R2" t="n">
-        <v>7246744</v>
+        <v>7246843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647124</v>
+        <v>122647154</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551916</v>
+        <v>552097</v>
       </c>
       <c r="R3" t="n">
-        <v>7246616</v>
+        <v>7246843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647127</v>
+        <v>122647149</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551916</v>
+        <v>551991</v>
       </c>
       <c r="R4" t="n">
-        <v>7246618</v>
+        <v>7246738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647154</v>
+        <v>122647128</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552097</v>
+        <v>551921</v>
       </c>
       <c r="R5" t="n">
-        <v>7246843</v>
+        <v>7246620</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647148</v>
+        <v>122647150</v>
       </c>
       <c r="B7" t="n">
-        <v>78848</v>
+        <v>74868</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552005</v>
+        <v>552059</v>
       </c>
       <c r="R7" t="n">
-        <v>7246718</v>
+        <v>7246774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647149</v>
+        <v>122647125</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>90966</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551991</v>
+        <v>551928</v>
       </c>
       <c r="R8" t="n">
-        <v>7246738</v>
+        <v>7246605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647131</v>
+        <v>122647143</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551931</v>
+        <v>551975</v>
       </c>
       <c r="R9" t="n">
-        <v>7246621</v>
+        <v>7246695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647129</v>
+        <v>122647167</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551975</v>
+        <v>552013</v>
       </c>
       <c r="R10" t="n">
-        <v>7246676</v>
+        <v>7246741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647170</v>
+        <v>122647151</v>
       </c>
       <c r="B11" t="n">
-        <v>74855</v>
+        <v>90970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552046</v>
+        <v>552083</v>
       </c>
       <c r="R11" t="n">
-        <v>7246745</v>
+        <v>7246812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647143</v>
+        <v>122647173</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551975</v>
+        <v>552049</v>
       </c>
       <c r="R12" t="n">
-        <v>7246695</v>
+        <v>7246747</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647153</v>
+        <v>122647181</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>90948</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552097</v>
+        <v>552065</v>
       </c>
       <c r="R13" t="n">
-        <v>7246843</v>
+        <v>7246777</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647152</v>
+        <v>122647124</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>552078</v>
+        <v>551916</v>
       </c>
       <c r="R14" t="n">
-        <v>7246829</v>
+        <v>7246616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647150</v>
+        <v>122647152</v>
       </c>
       <c r="B15" t="n">
-        <v>74868</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552059</v>
+        <v>552078</v>
       </c>
       <c r="R15" t="n">
-        <v>7246774</v>
+        <v>7246829</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647167</v>
+        <v>122647130</v>
       </c>
       <c r="B16" t="n">
-        <v>90952</v>
+        <v>78845</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>552013</v>
+        <v>551971</v>
       </c>
       <c r="R16" t="n">
-        <v>7246741</v>
+        <v>7246700</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647181</v>
+        <v>122647127</v>
       </c>
       <c r="B17" t="n">
-        <v>90948</v>
+        <v>82553</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>552065</v>
+        <v>551916</v>
       </c>
       <c r="R17" t="n">
-        <v>7246777</v>
+        <v>7246618</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647130</v>
+        <v>122647131</v>
       </c>
       <c r="B18" t="n">
-        <v>78848</v>
+        <v>90952</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551971</v>
+        <v>551931</v>
       </c>
       <c r="R18" t="n">
-        <v>7246700</v>
+        <v>7246621</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647128</v>
+        <v>122647170</v>
       </c>
       <c r="B19" t="n">
-        <v>90970</v>
+        <v>74855</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551921</v>
+        <v>552046</v>
       </c>
       <c r="R19" t="n">
-        <v>7246620</v>
+        <v>7246745</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647173</v>
+        <v>122647148</v>
       </c>
       <c r="B20" t="n">
-        <v>90948</v>
+        <v>78845</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552049</v>
+        <v>552005</v>
       </c>
       <c r="R20" t="n">
-        <v>7246747</v>
+        <v>7246718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647125</v>
+        <v>122647174</v>
       </c>
       <c r="B21" t="n">
-        <v>90966</v>
+        <v>82553</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2705,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551928</v>
+        <v>552044</v>
       </c>
       <c r="R21" t="n">
-        <v>7246605</v>
+        <v>7246744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647151</v>
+        <v>122647129</v>
       </c>
       <c r="B22" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>552083</v>
+        <v>551975</v>
       </c>
       <c r="R22" t="n">
-        <v>7246812</v>
+        <v>7246676</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647151</v>
+        <v>122647173</v>
       </c>
       <c r="B11" t="n">
-        <v>90970</v>
+        <v>90948</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552083</v>
+        <v>552049</v>
       </c>
       <c r="R11" t="n">
-        <v>7246812</v>
+        <v>7246747</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647173</v>
+        <v>122647181</v>
       </c>
       <c r="B12" t="n">
         <v>90948</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552049</v>
+        <v>552065</v>
       </c>
       <c r="R12" t="n">
-        <v>7246747</v>
+        <v>7246777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647181</v>
+        <v>122647151</v>
       </c>
       <c r="B13" t="n">
-        <v>90948</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552065</v>
+        <v>552083</v>
       </c>
       <c r="R13" t="n">
-        <v>7246777</v>
+        <v>7246812</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647153</v>
+        <v>122647128</v>
       </c>
       <c r="B2" t="n">
-        <v>79876</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552097</v>
+        <v>551921</v>
       </c>
       <c r="R2" t="n">
-        <v>7246843</v>
+        <v>7246620</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122647149</v>
+        <v>122647148</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78845</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551991</v>
+        <v>552005</v>
       </c>
       <c r="R4" t="n">
-        <v>7246738</v>
+        <v>7246718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647128</v>
+        <v>122647149</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551921</v>
+        <v>551991</v>
       </c>
       <c r="R5" t="n">
-        <v>7246620</v>
+        <v>7246738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647142</v>
+        <v>122647150</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>74868</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551988</v>
+        <v>552059</v>
       </c>
       <c r="R6" t="n">
-        <v>7246686</v>
+        <v>7246774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647150</v>
+        <v>122647167</v>
       </c>
       <c r="B7" t="n">
-        <v>74868</v>
+        <v>90952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552059</v>
+        <v>552013</v>
       </c>
       <c r="R7" t="n">
-        <v>7246774</v>
+        <v>7246741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647143</v>
+        <v>122647170</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>74855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551975</v>
+        <v>552046</v>
       </c>
       <c r="R9" t="n">
-        <v>7246695</v>
+        <v>7246745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647167</v>
+        <v>122647129</v>
       </c>
       <c r="B10" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552013</v>
+        <v>551975</v>
       </c>
       <c r="R10" t="n">
-        <v>7246741</v>
+        <v>7246676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647173</v>
+        <v>122647131</v>
       </c>
       <c r="B11" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>552049</v>
+        <v>551931</v>
       </c>
       <c r="R11" t="n">
-        <v>7246747</v>
+        <v>7246621</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647181</v>
+        <v>122647130</v>
       </c>
       <c r="B12" t="n">
-        <v>90948</v>
+        <v>78845</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>552065</v>
+        <v>551971</v>
       </c>
       <c r="R12" t="n">
-        <v>7246777</v>
+        <v>7246700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647151</v>
+        <v>122647152</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552083</v>
+        <v>552078</v>
       </c>
       <c r="R13" t="n">
-        <v>7246812</v>
+        <v>7246829</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647152</v>
+        <v>122647173</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>90948</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2069,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552078</v>
+        <v>552049</v>
       </c>
       <c r="R15" t="n">
-        <v>7246829</v>
+        <v>7246747</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647130</v>
+        <v>122647127</v>
       </c>
       <c r="B16" t="n">
-        <v>78845</v>
+        <v>82553</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551971</v>
+        <v>551916</v>
       </c>
       <c r="R16" t="n">
-        <v>7246700</v>
+        <v>7246618</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647127</v>
+        <v>122647143</v>
       </c>
       <c r="B17" t="n">
-        <v>82553</v>
+        <v>90970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551916</v>
+        <v>551975</v>
       </c>
       <c r="R17" t="n">
-        <v>7246618</v>
+        <v>7246695</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647131</v>
+        <v>122647181</v>
       </c>
       <c r="B18" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2387,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551931</v>
+        <v>552065</v>
       </c>
       <c r="R18" t="n">
-        <v>7246621</v>
+        <v>7246777</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647170</v>
+        <v>122647151</v>
       </c>
       <c r="B19" t="n">
-        <v>74855</v>
+        <v>90970</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552046</v>
+        <v>552083</v>
       </c>
       <c r="R19" t="n">
-        <v>7246745</v>
+        <v>7246812</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647148</v>
+        <v>122647142</v>
       </c>
       <c r="B20" t="n">
-        <v>78845</v>
+        <v>90970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>552005</v>
+        <v>551988</v>
       </c>
       <c r="R20" t="n">
-        <v>7246718</v>
+        <v>7246686</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122647129</v>
+        <v>122647153</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>551975</v>
+        <v>552097</v>
       </c>
       <c r="R22" t="n">
-        <v>7246676</v>
+        <v>7246843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14810-2023 artfynd.xlsx
+++ b/artfynd/A 14810-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122647128</v>
+        <v>122647170</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551921</v>
+        <v>552046</v>
       </c>
       <c r="R2" t="n">
-        <v>7246620</v>
+        <v>7246745</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122647154</v>
+        <v>122647130</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552097</v>
+        <v>551971</v>
       </c>
       <c r="R3" t="n">
-        <v>7246843</v>
+        <v>7246700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -890,12 +880,7 @@
         <v>122647148</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122647149</v>
+        <v>122647173</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551991</v>
+        <v>552049</v>
       </c>
       <c r="R5" t="n">
-        <v>7246738</v>
+        <v>7246747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122647150</v>
+        <v>122647181</v>
       </c>
       <c r="B6" t="n">
-        <v>74868</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552059</v>
+        <v>552065</v>
       </c>
       <c r="R6" t="n">
-        <v>7246774</v>
+        <v>7246777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1169,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122647167</v>
+        <v>122647131</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552013</v>
+        <v>551931</v>
       </c>
       <c r="R7" t="n">
-        <v>7246741</v>
+        <v>7246621</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122647125</v>
+        <v>122647167</v>
       </c>
       <c r="B8" t="n">
-        <v>90966</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551928</v>
+        <v>552013</v>
       </c>
       <c r="R8" t="n">
-        <v>7246605</v>
+        <v>7246741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122647170</v>
+        <v>122647125</v>
       </c>
       <c r="B9" t="n">
-        <v>74855</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552046</v>
+        <v>551928</v>
       </c>
       <c r="R9" t="n">
-        <v>7246745</v>
+        <v>7246605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122647129</v>
+        <v>122647127</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551975</v>
+        <v>551916</v>
       </c>
       <c r="R10" t="n">
-        <v>7246676</v>
+        <v>7246618</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1573,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hannah Norman</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122647131</v>
+        <v>122647174</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551931</v>
+        <v>552044</v>
       </c>
       <c r="R11" t="n">
-        <v>7246621</v>
+        <v>7246744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122647130</v>
+        <v>122647150</v>
       </c>
       <c r="B12" t="n">
-        <v>78845</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551971</v>
+        <v>552059</v>
       </c>
       <c r="R12" t="n">
-        <v>7246700</v>
+        <v>7246774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122647152</v>
+        <v>122647154</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>552078</v>
+        <v>552097</v>
       </c>
       <c r="R13" t="n">
-        <v>7246829</v>
+        <v>7246843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,19 +1887,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122647124</v>
+        <v>122647122</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1987,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551916</v>
+        <v>551874</v>
       </c>
       <c r="R14" t="n">
-        <v>7246616</v>
+        <v>7246567</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,37 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122647173</v>
+        <v>122647124</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>552049</v>
+        <v>551916</v>
       </c>
       <c r="R15" t="n">
-        <v>7246747</v>
+        <v>7246616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2078,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,37 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122647127</v>
+        <v>122647129</v>
       </c>
       <c r="B16" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>551916</v>
+        <v>551975</v>
       </c>
       <c r="R16" t="n">
-        <v>7246618</v>
+        <v>7246676</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2179,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,37 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122647143</v>
+        <v>122647149</v>
       </c>
       <c r="B17" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551975</v>
+        <v>551991</v>
       </c>
       <c r="R17" t="n">
-        <v>7246695</v>
+        <v>7246738</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2280,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,37 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122647181</v>
+        <v>122647152</v>
       </c>
       <c r="B18" t="n">
-        <v>90948</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>552065</v>
+        <v>552078</v>
       </c>
       <c r="R18" t="n">
-        <v>7246777</v>
+        <v>7246829</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2381,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2477,37 +2392,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122647151</v>
+        <v>122647153</v>
       </c>
       <c r="B19" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>552083</v>
+        <v>552097</v>
       </c>
       <c r="R19" t="n">
-        <v>7246812</v>
+        <v>7246843</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122647142</v>
+        <v>122647123</v>
       </c>
       <c r="B20" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551988</v>
+        <v>551884</v>
       </c>
       <c r="R20" t="n">
-        <v>7246686</v>
+        <v>7246571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2583,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2689,15 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122647174</v>
+        <v>122647155</v>
       </c>
       <c r="B21" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2705,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>552044</v>
+        <v>552076</v>
       </c>
       <c r="R21" t="n">
-        <v>7246744</v>
+        <v>7246876</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,116 +2684,10 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Hannah Norman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
-        <is>
-          <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>122647153</v>
-      </c>
-      <c r="B22" t="n">
-        <v>79876</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Dikanäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>552097</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7246843</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Mika Thunell</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Hannah Norman</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
         <is>
           <t>EEN0089 Ajaure-Dikanäs NVI 2024</t>
         </is>
